--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6062,10 +6062,8 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333 </t>
-        </is>
+      <c r="A179" t="n">
+        <v>333</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -6096,6 +6094,40 @@
       <c r="H179" t="inlineStr">
         <is>
           <t>Seth Charley</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">329 </t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Kelsey Bryant</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D180" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="E180" s="1" t="n">
+        <v>46360.99930555555</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>329 - Chevy Trail Boss, White</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Kelsey Bryant</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6098,10 +6098,8 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">329 </t>
-        </is>
+      <c r="A180" t="n">
+        <v>329</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -6128,6 +6126,44 @@
       <c r="H180" t="inlineStr">
         <is>
           <t>Kelsey Bryant</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">333 </t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Anita Joy Antoninka</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D181" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E181" s="1" t="n">
+        <v>46289.99930555555</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>333 - 2017 Toyota Tacoma, Charcoal (5 Seats)</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>field work at north rim of gc. no dirt roads, just space for gear and people</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Seth Charley</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H181"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5999,11 +5999,11 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>OUT OF COMMISSION</t>
+          <t>Salli Dymond</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6012,30 +6012,30 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E177" s="1" t="n">
         <v>46276.99930555555</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>268 - 2017 Ford F-150, Silver(6 Seats)</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Needs oil change asap</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr"/>
+          <t>332 - 2009 Dodge Dakota, White (5 Seats)</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Cody Folk</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Salli Dymond</t>
+          <t>Anita Joy Antoninka</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6044,30 +6044,34 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46274</v>
+        <v>46280</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46276.99930555555</v>
+        <v>46289.99930555555</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>332 - 2009 Dodge Dakota, White (5 Seats)</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr"/>
+          <t>333 - 2017 Toyota Tacoma, Charcoal (5 Seats)</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>field work at north rim of gc. no dirt roads, just space for gear and people</t>
+        </is>
+      </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Cody Folk</t>
+          <t>Seth Charley</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Anita Joy Antoninka</t>
+          <t>Kelsey Bryant</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6076,34 +6080,30 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289.99930555555</v>
+        <v>46360.99930555555</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>333 - 2017 Toyota Tacoma, Charcoal (5 Seats)</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>field work at north rim of gc. no dirt roads, just space for gear and people</t>
-        </is>
-      </c>
+          <t>329 - Chevy Trail Boss, White</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Seth Charley</t>
+          <t>Kelsey Bryant</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Kelsey Bryant</t>
+          <t>Anita Joy Antoninka</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6112,56 +6112,22 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46360.99930555555</v>
+        <v>46289.99930555555</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>329 - Chevy Trail Boss, White</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr"/>
+          <t>333 - 2017 Toyota Tacoma, Charcoal (5 Seats)</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>field work at north rim of gc. no dirt roads, just space for gear and people</t>
+        </is>
+      </c>
       <c r="H180" t="inlineStr">
-        <is>
-          <t>Kelsey Bryant</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333 </t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Anita Joy Antoninka</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="D181" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="E181" s="1" t="n">
-        <v>46289.99930555555</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>333 - 2017 Toyota Tacoma, Charcoal (5 Seats)</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>field work at north rim of gc. no dirt roads, just space for gear and people</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
         <is>
           <t>Seth Charley</t>
         </is>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6133,6 +6133,40 @@
         </is>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321 </t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Anita Joy Antoninka</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D181" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="E181" s="1" t="n">
+        <v>46285.99930555555</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>321 - Chevy Trail Boss, White</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Mariola Barerra</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H181"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6134,10 +6134,8 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321 </t>
-        </is>
+      <c r="A181" t="n">
+        <v>321</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -6166,6 +6164,40 @@
           <t>Mariola Barerra</t>
         </is>
       </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">330 </t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>OUT OF COMMISSION</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D182" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E182" s="1" t="n">
+        <v>46285.99930555555</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>330 - Toyota Camry</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Getting Bumper Fixed</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6166,10 +6166,8 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">330 </t>
-        </is>
+      <c r="A182" t="n">
+        <v>330</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -6198,6 +6196,40 @@
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">333 </t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Kristen Waring</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Reserved</t>
+        </is>
+      </c>
+      <c r="D183" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="E183" s="1" t="n">
+        <v>46290.99930555555</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>333 - 2017 Toyota Tacoma, Charcoal (5 Seats)</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Abirel Acharya</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6197,40 +6197,6 @@
       </c>
       <c r="H182" t="inlineStr"/>
     </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333 </t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Kristen Waring</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Reserved</t>
-        </is>
-      </c>
-      <c r="D183" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="E183" s="1" t="n">
-        <v>46290.99930555555</v>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>333 - 2017 Toyota Tacoma, Charcoal (5 Seats)</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Abirel Acharya</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6197,6 +6197,40 @@
       </c>
       <c r="H182" t="inlineStr"/>
     </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268 </t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Kristen Waring</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D183" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="E183" s="1" t="n">
+        <v>46290.99930555555</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>268 - 2017 Ford F-150, Silver(6 Seats)</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Abirel Acharya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H183"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6198,10 +6198,8 @@
       <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268 </t>
-        </is>
+      <c r="A183" t="n">
+        <v>268</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -6228,6 +6226,44 @@
       <c r="H183" t="inlineStr">
         <is>
           <t>Abirel Acharya</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321 </t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Jill Beckmann</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D184" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="E184" s="1" t="n">
+        <v>46290.99930555555</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>321 - Chevy Trail Boss, White</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>FOR 211 on Thursday - will drive 2 miles; Provost Visit on Friday - will drive to Centennial Forest ~ 30 miles</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Jill Beckmann, Villette Barlow</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6230,10 +6230,8 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321 </t>
-        </is>
+      <c r="A184" t="n">
+        <v>321</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -6264,6 +6262,44 @@
       <c r="H184" t="inlineStr">
         <is>
           <t>Jill Beckmann, Villette Barlow</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">330 </t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Matthew Bowker</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D185" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="E185" s="1" t="n">
+        <v>46326.99930555555</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>330 - Toyota Camry</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I will be in town to arrange CrustNet-related field work and to make one trip to Moab, UT to drop off equipment and samples. I will request separate trucks for the field work, so this request is just for my in-town work responsibilities AND the trip to Moab, UT. My return date for the vehicle is likely 10/28, but I put the end of the month here just in case something comes up and the trip home is delayed. </t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sierra Gugel</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6266,10 +6266,8 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">330 </t>
-        </is>
+      <c r="A185" t="n">
+        <v>330</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -6298,6 +6296,44 @@
         </is>
       </c>
       <c r="H185" t="inlineStr">
+        <is>
+          <t>Sierra Gugel</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">332 </t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Matthew Bowker</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D186" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="E186" s="1" t="n">
+        <v>46315.99930555555</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>332 - 2009 Dodge Dakota, White (5 Seats)</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I will be traveling with at least two NAU-associated workers to a field site in New Mexico. </t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
         <is>
           <t>Sierra Gugel</t>
         </is>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6302,10 +6302,8 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">332 </t>
-        </is>
+      <c r="A186" t="n">
+        <v>332</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -6336,6 +6334,44 @@
       <c r="H186" t="inlineStr">
         <is>
           <t>Sierra Gugel</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268 </t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Matthew Bowker</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D187" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="E187" s="1" t="n">
+        <v>46293.99930555555</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>268 - 2017 Ford F-150, Silver(6 Seats)</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">We will be traveling for field work in California on dirt roads. We need a 4WD vehicle with high clearance. Total number of occupants may be 5-6 people. We will have a lot of gear and equipment. </t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Seth Charley, Sierra Gugel</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H187"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6337,44 +6337,6 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268 </t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Matthew Bowker</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="D187" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="E187" s="1" t="n">
-        <v>46293.99930555555</v>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>268 - 2017 Ford F-150, Silver(6 Seats)</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">We will be traveling for field work in California on dirt roads. We need a 4WD vehicle with high clearance. Total number of occupants may be 5-6 people. We will have a lot of gear and equipment. </t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Seth Charley, Sierra Gugel</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6337,6 +6337,44 @@
         </is>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268 </t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Matthew Bowker</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D187" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="E187" s="1" t="n">
+        <v>46323.99930555555</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>268 - 2017 Ford F-150, Silver(6 Seats)</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">We will be traveling for field work in California on dirt roads. We need a 4WD vehicle with high clearance. Total number of occupants may be 5-6 people. We will have a lot of gear and equipment. </t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Seth Charley, Sierra Gugel</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H187"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6338,10 +6338,8 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268 </t>
-        </is>
+      <c r="A187" t="n">
+        <v>268</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -6372,6 +6370,44 @@
       <c r="H187" t="inlineStr">
         <is>
           <t>Seth Charley, Sierra Gugel</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Anita Joy Antoninka</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D188" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="E188" s="1" t="n">
+        <v>46314.99930555555</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>331- 2024  Toyota Sienna Hybrid, White (8 seats)</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>to and from mesa airport</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Anita Antoninka, Matthew Bowker</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6374,10 +6374,8 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
+      <c r="A188" t="n">
+        <v>331</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -6408,6 +6406,40 @@
       <c r="H188" t="inlineStr">
         <is>
           <t>Anita Antoninka, Matthew Bowker</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">333 </t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Anita Joy Antoninka</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D189" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="E189" s="1" t="n">
+        <v>46303.99930555555</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>333 - 2017 Toyota Tacoma, Charcoal (5 Seats)</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Seth Charley</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H189"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6410,10 +6410,8 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333 </t>
-        </is>
+      <c r="A189" t="n">
+        <v>333</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -6440,6 +6438,40 @@
       <c r="H189" t="inlineStr">
         <is>
           <t>Seth Charley</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">330 </t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Georgia Roberts</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D190" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E190" s="1" t="n">
+        <v>46295.99930555555</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>330 - Toyota Camry</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Caelin Dicke</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6442,10 +6442,8 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">330 </t>
-        </is>
+      <c r="A190" t="n">
+        <v>330</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -6470,6 +6468,40 @@
       </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
+        <is>
+          <t>Caelin Dicke</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">330 </t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Georgia Roberts</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D191" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E191" s="1" t="n">
+        <v>46300.99930555555</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>330 - Toyota Camry</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr">
         <is>
           <t>Caelin Dicke</t>
         </is>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H191"/>
+  <dimension ref="A1:H192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6474,10 +6474,8 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">330 </t>
-        </is>
+      <c r="A191" t="n">
+        <v>330</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -6504,6 +6502,40 @@
       <c r="H191" t="inlineStr">
         <is>
           <t>Caelin Dicke</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321 </t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Jill Beckmann</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D192" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="E192" s="1" t="n">
+        <v>46297.99930555555</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>321 - Chevy Trail Boss, White</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Jill Beckmann</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:H193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6506,10 +6506,8 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321 </t>
-        </is>
+      <c r="A192" t="n">
+        <v>321</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -6536,6 +6534,40 @@
       <c r="H192" t="inlineStr">
         <is>
           <t>Jill Beckmann</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Anita Joy Antoninka</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D193" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="E193" s="1" t="n">
+        <v>46325.99930555555</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>331- 2024  Toyota Sienna Hybrid, White (8 seats)</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Anita Antoninka</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H193"/>
+  <dimension ref="A1:H194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6538,10 +6538,8 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
+      <c r="A193" t="n">
+        <v>331</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -6568,6 +6566,40 @@
       <c r="H193" t="inlineStr">
         <is>
           <t>Anita Antoninka</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">330 </t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Salli Dymond</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D194" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E194" s="1" t="n">
+        <v>46304.99930555555</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>330 - Toyota Camry</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Cody Folk</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H194"/>
+  <dimension ref="A1:H195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6570,10 +6570,8 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">330 </t>
-        </is>
+      <c r="A194" t="n">
+        <v>330</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -6600,6 +6598,40 @@
       <c r="H194" t="inlineStr">
         <is>
           <t>Cody Folk</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268 </t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Kristen Waring</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D195" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="E195" s="1" t="n">
+        <v>46308.99930555555</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>268 - 2017 Ford F-150, Silver(6 Seats)</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Abirel Acharya</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H195"/>
+  <dimension ref="A1:H196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6602,10 +6602,8 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268 </t>
-        </is>
+      <c r="A195" t="n">
+        <v>268</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -6632,6 +6630,40 @@
       <c r="H195" t="inlineStr">
         <is>
           <t>Abirel Acharya</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">333 </t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Georgia Roberts</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D196" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="E196" s="1" t="n">
+        <v>46307.99930555555</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>333 - 2017 Toyota Tacoma, Charcoal (5 Seats)</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Caelin Dicke</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H196"/>
+  <dimension ref="A1:H197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6634,10 +6634,8 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333 </t>
-        </is>
+      <c r="A196" t="n">
+        <v>333</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -6664,6 +6662,40 @@
       <c r="H196" t="inlineStr">
         <is>
           <t>Caelin Dicke</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321 </t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Salli Dymond</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D197" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="E197" s="1" t="n">
+        <v>46302.99930555555</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>321 - Chevy Trail Boss, White</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Cody Folk</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H197"/>
+  <dimension ref="A1:H198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6666,10 +6666,8 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321 </t>
-        </is>
+      <c r="A197" t="n">
+        <v>321</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -6696,6 +6694,40 @@
       <c r="H197" t="inlineStr">
         <is>
           <t>Cody Folk</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321 </t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Salli Dymond</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D198" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="E198" s="1" t="n">
+        <v>46314.99930555555</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>321 - Chevy Trail Boss, White</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Emory Ellis</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H198"/>
+  <dimension ref="A1:H199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6698,10 +6698,8 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321 </t>
-        </is>
+      <c r="A198" t="n">
+        <v>321</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -6728,6 +6726,40 @@
       <c r="H198" t="inlineStr">
         <is>
           <t>Emory Ellis</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">333 </t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Georgia Roberts</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D199" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="E199" s="1" t="n">
+        <v>46310.99930555555</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>333 - 2017 Toyota Tacoma, Charcoal (5 Seats)</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Caelin Dicke</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H199"/>
+  <dimension ref="A1:H200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6730,10 +6730,8 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333 </t>
-        </is>
+      <c r="A199" t="n">
+        <v>333</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -6758,6 +6756,40 @@
       </c>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr">
+        <is>
+          <t>Caelin Dicke</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268 </t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Georgia Roberts</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D200" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="E200" s="1" t="n">
+        <v>46314.99930555555</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>268 - 2017 Ford F-150, Silver(6 Seats)</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr">
         <is>
           <t>Caelin Dicke</t>
         </is>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H200"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6762,10 +6762,8 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268 </t>
-        </is>
+      <c r="A200" t="n">
+        <v>268</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -6792,6 +6790,40 @@
       <c r="H200" t="inlineStr">
         <is>
           <t>Caelin Dicke</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">333 </t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Jill Beckmann</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D201" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="E201" s="1" t="n">
+        <v>46310.99930555555</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>333 - 2017 Toyota Tacoma, Charcoal (5 Seats)</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Jill Beckmann</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H201"/>
+  <dimension ref="A1:H200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6793,40 +6793,6 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333 </t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Jill Beckmann</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
-        </is>
-      </c>
-      <c r="D201" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="E201" s="1" t="n">
-        <v>46310.99930555555</v>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>333 - 2017 Toyota Tacoma, Charcoal (5 Seats)</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Jill Beckmann</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H200"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6793,6 +6793,40 @@
         </is>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">333 </t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Anita Joy Antoninka</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D201" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="E201" s="1" t="n">
+        <v>46321.99930555555</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>333 - 2017 Toyota Tacoma, Charcoal (5 Seats)</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Benjamin Covington</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H201"/>
+  <dimension ref="A1:H202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6794,10 +6794,8 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333 </t>
-        </is>
+      <c r="A201" t="n">
+        <v>333</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -6824,6 +6822,40 @@
       <c r="H201" t="inlineStr">
         <is>
           <t>Benjamin Covington</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">332 </t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Georgia Roberts</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D202" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="E202" s="1" t="n">
+        <v>46318.99930555555</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>332 - 2009 Dodge Dakota, White (5 Seats)</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Caelin Dicke</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H202"/>
+  <dimension ref="A1:H203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6826,10 +6826,8 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">332 </t>
-        </is>
+      <c r="A202" t="n">
+        <v>332</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -6856,6 +6854,40 @@
       <c r="H202" t="inlineStr">
         <is>
           <t>Caelin Dicke</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Jill Beckmann</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D203" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="E203" s="1" t="n">
+        <v>46321.99930555555</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>331- 2024  Toyota Sienna Hybrid, White (8 seats)</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Cameron Davis</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H203"/>
+  <dimension ref="A1:H204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6858,10 +6858,8 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
+      <c r="A203" t="n">
+        <v>331</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -6886,6 +6884,40 @@
       </c>
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
+        <is>
+          <t>Cameron Davis</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321 </t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Jill Beckmann</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D204" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="E204" s="1" t="n">
+        <v>46321.99930555555</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>321 - Chevy Trail Boss, White</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr">
         <is>
           <t>Cameron Davis</t>
         </is>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H204"/>
+  <dimension ref="A1:H205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6890,10 +6890,8 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321 </t>
-        </is>
+      <c r="A204" t="n">
+        <v>321</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -6920,6 +6918,40 @@
       <c r="H204" t="inlineStr">
         <is>
           <t>Cameron Davis</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">321 </t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Jill Beckmann</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D205" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="E205" s="1" t="n">
+        <v>46323.99930555555</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>321 - Chevy Trail Boss, White</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Jill Beckmann</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H205"/>
+  <dimension ref="A1:H206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6922,10 +6922,8 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321 </t>
-        </is>
+      <c r="A205" t="n">
+        <v>321</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -6950,6 +6948,40 @@
       </c>
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
+        <is>
+          <t>Jill Beckmann</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">332 </t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Jill Beckmann</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D206" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="E206" s="1" t="n">
+        <v>46323.99930555555</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>332 - 2009 Dodge Dakota, White (5 Seats)</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
         <is>
           <t>Jill Beckmann</t>
         </is>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H206"/>
+  <dimension ref="A1:H207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6954,10 +6954,8 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t xml:space="preserve">332 </t>
-        </is>
+      <c r="A206" t="n">
+        <v>332</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -6984,6 +6982,40 @@
       <c r="H206" t="inlineStr">
         <is>
           <t>Jill Beckmann</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">330 </t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Georgia Roberts</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D207" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="E207" s="1" t="n">
+        <v>46328.99930555555</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>330 - Toyota Camry</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Caelin Dicke</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H207"/>
+  <dimension ref="A1:H208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6986,10 +6986,8 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t xml:space="preserve">330 </t>
-        </is>
+      <c r="A207" t="n">
+        <v>330</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -7016,6 +7014,40 @@
       <c r="H207" t="inlineStr">
         <is>
           <t>Caelin Dicke</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">330 </t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Seafha Ramos</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D208" s="1" t="n">
+        <v>46331</v>
+      </c>
+      <c r="E208" s="1" t="n">
+        <v>46350.99930555555</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>330 - Toyota Camry</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Seafha Ramos</t>
         </is>
       </c>
     </row>

--- a/Vehicle_Checkout_List.xlsx
+++ b/Vehicle_Checkout_List.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H208"/>
+  <dimension ref="A1:H209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7018,10 +7018,8 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t xml:space="preserve">330 </t>
-        </is>
+      <c r="A208" t="n">
+        <v>330</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -7048,6 +7046,40 @@
       <c r="H208" t="inlineStr">
         <is>
           <t>Seafha Ramos</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">333 </t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Salli Dymond</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D209" s="1" t="n">
+        <v>46328</v>
+      </c>
+      <c r="E209" s="1" t="n">
+        <v>46329.99930555555</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>333 - 2017 Toyota Tacoma, Charcoal (5 Seats)</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Cody Folk</t>
         </is>
       </c>
     </row>
